--- a/assets/accessibility-report-template.xlsx
+++ b/assets/accessibility-report-template.xlsx
@@ -24,168 +24,168 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="369">
   <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>SC1</t>
+  </si>
+  <si>
+    <t>Level1</t>
+  </si>
+  <si>
+    <t>Synopsis1</t>
+  </si>
+  <si>
+    <t>Understanding1</t>
+  </si>
+  <si>
+    <t>SC2</t>
+  </si>
+  <si>
+    <t>Level2</t>
+  </si>
+  <si>
+    <t>Synopsis2</t>
+  </si>
+  <si>
+    <t>Understanding2</t>
+  </si>
+  <si>
+    <t>SC3</t>
+  </si>
+  <si>
+    <t>Level3</t>
+  </si>
+  <si>
+    <t>Synopsis3</t>
+  </si>
+  <si>
+    <t>Understanding3</t>
+  </si>
+  <si>
+    <t>Links</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Screengrab</t>
+  </si>
+  <si>
     <t>WCAG 2.2 Accessibility Issues Overview (Please note that single issues can fail multiple success criteria)</t>
   </si>
   <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>SC1</t>
-  </si>
-  <si>
-    <t>Level1</t>
-  </si>
-  <si>
-    <t>Synopsis1</t>
-  </si>
-  <si>
-    <t>Understanding1</t>
-  </si>
-  <si>
-    <t>SC2</t>
-  </si>
-  <si>
-    <t>Level2</t>
-  </si>
-  <si>
-    <t>Synopsis2</t>
-  </si>
-  <si>
-    <t>Understanding2</t>
-  </si>
-  <si>
-    <t>SC3</t>
-  </si>
-  <si>
-    <t>Level3</t>
-  </si>
-  <si>
-    <t>Synopsis3</t>
-  </si>
-  <si>
-    <t>Understanding3</t>
-  </si>
-  <si>
-    <t>Links</t>
-  </si>
-  <si>
-    <t>Summary</t>
-  </si>
-  <si>
-    <t>Environment</t>
-  </si>
-  <si>
-    <t>Issue</t>
-  </si>
-  <si>
-    <t>Testing</t>
-  </si>
-  <si>
-    <t>Screengrab</t>
+    <t>Translation?</t>
+  </si>
+  <si>
+    <t>ProductNote</t>
+  </si>
+  <si>
+    <t>Labels</t>
+  </si>
+  <si>
+    <t>Impact</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assignment</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
+    <t>JIRASeverity</t>
+  </si>
+  <si>
+    <t>Specialist</t>
+  </si>
+  <si>
+    <t>Implementation</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>JIRA</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>A11YEXP001</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Translation?</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
     <t>Critical</t>
   </si>
   <si>
-    <t>ProductNote</t>
-  </si>
-  <si>
-    <t>Labels</t>
+    <t>1.1.1: Non-text Content - Level A</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Success Criteria</t>
   </si>
   <si>
     <t>Serious</t>
   </si>
   <si>
-    <t>Impact</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Moderate</t>
   </si>
   <si>
-    <t>Assignment</t>
-  </si>
-  <si>
     <t>Minor</t>
   </si>
   <si>
-    <t>Effort</t>
-  </si>
-  <si>
-    <t>JIRASeverity</t>
-  </si>
-  <si>
-    <t>Specialist</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>Implementation</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>JIRA</t>
-  </si>
-  <si>
-    <t>Estimate</t>
+    <t xml:space="preserve"> Level</t>
   </si>
   <si>
     <t>AA</t>
   </si>
   <si>
-    <t>A11YEXP001</t>
-  </si>
-  <si>
     <t>AAA</t>
   </si>
   <si>
     <t>BP</t>
   </si>
   <si>
+    <t xml:space="preserve"> Synopsis</t>
+  </si>
+  <si>
     <t>Auto</t>
   </si>
   <si>
+    <t xml:space="preserve"> Understanding</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>Total Issues</t>
   </si>
   <si>
+    <t>NA</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ticket URL:   </t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>1.1.1: Non-text Content - Level A</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Success Criteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Synopsis</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Understanding</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Provide text alternatives for non-text content</t>
   </si>
   <si>
@@ -201,18 +201,18 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/audio-only-and-video-only-prerecorded</t>
   </si>
   <si>
+    <t>1.2.2: Captions (Prerecorded) - Level A</t>
+  </si>
+  <si>
+    <t>Provide captions for videos with audio</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/captions-prerecorded</t>
+  </si>
+  <si>
     <t>4.1.2: Name, Role, Value - Level A</t>
   </si>
   <si>
-    <t>1.2.2: Captions (Prerecorded) - Level A</t>
-  </si>
-  <si>
-    <t>Provide captions for videos with audio</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/captions-prerecorded</t>
-  </si>
-  <si>
     <t>1.2.3: Audio Description or Media Alternative (Prerecorded) - Level A</t>
   </si>
   <si>
@@ -220,9 +220,6 @@
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/audio-description-or-media-alternative-prerecorded</t>
-  </si>
-  <si>
-    <t>Automated Scan (AXE)</t>
   </si>
   <si>
     <t>1.3.1: Info and Relationships - Level A</t>
@@ -258,10 +255,25 @@
     </r>
   </si>
   <si>
+    <t>Automated Scan (AXE)</t>
+  </si>
+  <si>
     <t>1.3.2: Meaningful Sequence - Level A</t>
   </si>
   <si>
     <t>Present content in a meaningful order</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/meaningful-sequence</t>
+  </si>
+  <si>
+    <t>1.3.3: Sensory Characteristics - Level A</t>
+  </si>
+  <si>
+    <t>Use more than one sense for instructions. Instructions do not rely upon shape, size, visual location or audio</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/sensory-characteristics</t>
   </si>
   <si>
     <r>
@@ -285,18 +297,6 @@
     </r>
   </si>
   <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/meaningful-sequence</t>
-  </si>
-  <si>
-    <t>1.3.3: Sensory Characteristics - Level A</t>
-  </si>
-  <si>
-    <t>Use more than one sense for instructions. Instructions do not rely upon shape, size, visual location or audio</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/sensory-characteristics</t>
-  </si>
-  <si>
     <t>1.4.1: Use of Color - Level A</t>
   </si>
   <si>
@@ -306,10 +306,16 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/use-of-color</t>
   </si>
   <si>
+    <t>1.4.2: Audio Control - Level A</t>
+  </si>
+  <si>
+    <t>Don’t play audio automatically</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/audio-control</t>
+  </si>
+  <si>
     <t>Global: Company Logo Missing Alt Attribute and Value</t>
-  </si>
-  <si>
-    <t>1.4.2: Audio Control - Level A</t>
   </si>
   <si>
     <t>The client/company logo in the bottom-left navigation is missing an alt text attribute and value. This is an informative image, so it must be described to the user. Alt attributes must always be included, even if they have no value (called a "null" alt), otherwise the image path may be read out to AT, which is undesirable. 
@@ -319,10 +325,16 @@
  {code}&lt;img alt="Radancy Logo" width="182" height="45" class="sidenav_footer_logo" src="https://api.1brd.com/v1/companies/ce9bf599-f0b4-4a9e-969a-25df747610a9/logo" style="border-radius: 3px;"&gt;{code}</t>
   </si>
   <si>
-    <t>Don’t play audio automatically</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/audio-control</t>
+    <t>2.1.1: Keyboard - Level A</t>
+  </si>
+  <si>
+    <t>Accessible by keyboard only</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/keyboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delivery Date:  </t>
   </si>
   <si>
     <r>
@@ -372,252 +384,249 @@
     </r>
   </si>
   <si>
-    <t>2.1.1: Keyboard - Level A</t>
-  </si>
-  <si>
-    <t>Accessible by keyboard only</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/keyboard</t>
+    <t>Severity &amp; Levels by Assignment</t>
   </si>
   <si>
     <t>2.1.2: No Keyboard Trap - Level A</t>
   </si>
   <si>
+    <t xml:space="preserve">QA URL:  </t>
+  </si>
+  <si>
     <t>Don’t trap keyboard users</t>
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/no-keyboard-trap</t>
   </si>
   <si>
+    <t xml:space="preserve">Production URL:  </t>
+  </si>
+  <si>
     <t>2.1.4: Character Key Shortcuts - Level A</t>
   </si>
   <si>
-    <t xml:space="preserve">Delivery Date:  </t>
-  </si>
-  <si>
     <t>Ensure custom shortcuts include, or can be made to include, a modifier key.</t>
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/character-key-shortcuts</t>
   </si>
   <si>
-    <t>Severity &amp; Levels by Assignment</t>
+    <t xml:space="preserve">Target Guidelines:  </t>
+  </si>
+  <si>
+    <t>WCAG 2.2 AA (Includes Level A)</t>
   </si>
   <si>
     <t>2.2.1: Timing Adjustable - Level A</t>
   </si>
   <si>
-    <t xml:space="preserve">QA URL:  </t>
-  </si>
-  <si>
     <t>Time limits have user controls</t>
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/timing-adjustable</t>
   </si>
   <si>
-    <t>Accessibility Support</t>
+    <t xml:space="preserve">Development Support Traffic:  </t>
+  </si>
+  <si>
+    <t>2.2.2: Pause, Stop, Hide - Level A</t>
+  </si>
+  <si>
+    <t>Provide user controls for moving content</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/pause-stop-hide</t>
+  </si>
+  <si>
+    <t>2.3.1: Three Flashes or Below Threshold - Level A</t>
+  </si>
+  <si>
+    <t>No content flashes more than three times per second</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/three-flashes-or-below-threshold</t>
+  </si>
+  <si>
+    <t>Third-Party Issue (YouTube, ATS, etc.)</t>
+  </si>
+  <si>
+    <t>2.4.1: Bypass Blocks - Level A</t>
+  </si>
+  <si>
+    <t>Provide a ‘Skip to Content’ link</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/bypass-blocks</t>
   </si>
   <si>
     <t>Easy</t>
   </si>
   <si>
-    <t xml:space="preserve">Production URL:  </t>
-  </si>
-  <si>
-    <t>2.2.2: Pause, Stop, Hide - Level A</t>
-  </si>
-  <si>
-    <t>Provide user controls for moving content</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/pause-stop-hide</t>
-  </si>
-  <si>
-    <t>Fixed in Preview</t>
-  </si>
-  <si>
-    <t>2.3.1: Three Flashes or Below Threshold - Level A</t>
-  </si>
-  <si>
-    <t>No content flashes more than three times per second</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/three-flashes-or-below-threshold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target Guidelines:  </t>
+    <t>2.4.2: Page Titled - Level A</t>
+  </si>
+  <si>
+    <t>Use helpful and clear page titles</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/page-titled</t>
+  </si>
+  <si>
+    <t>2.4.3: Focus Order - Level A</t>
+  </si>
+  <si>
+    <t>Logical order</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/focus-order</t>
+  </si>
+  <si>
+    <t>2.4.4: Link Purpose (In Context) - Level A</t>
+  </si>
+  <si>
+    <t>Every link’s purpose is clear from its context</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/link-purpose-in-context</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>2.5.1: Pointer Gestures - Level A</t>
+  </si>
+  <si>
+    <t>Let users operate touchscreens with a single finger</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/pointer-gestures.html</t>
   </si>
   <si>
     <t>A11YEXP002</t>
   </si>
   <si>
-    <t>2.4.1: Bypass Blocks - Level A</t>
-  </si>
-  <si>
-    <t>Provide a ‘Skip to Content’ link</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/bypass-blocks</t>
-  </si>
-  <si>
-    <t>WCAG 2.2 AA (Includes Level A)</t>
-  </si>
-  <si>
-    <t>2.4.2: Page Titled - Level A</t>
-  </si>
-  <si>
-    <t>Use helpful and clear page titles</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/page-titled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Support Traffic:  </t>
+    <t>2.5.2: Pointer Cancellation - Level A</t>
+  </si>
+  <si>
+    <t>Reduce accidental activation of controls by making their operation consistent</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/pointer-cancellation</t>
+  </si>
+  <si>
+    <t>2.5.3: Label In Name - Level A</t>
+  </si>
+  <si>
+    <t>Let the visual label for controls be a trigger for speech activation.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/label-in-name</t>
+  </si>
+  <si>
+    <t>2.5.4: Motion Actuation - Level A</t>
+  </si>
+  <si>
+    <t>Don’t rely solely on device motion to control page content</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/motion-actuation</t>
+  </si>
+  <si>
+    <t>3.1.1: Language of Page - Level A</t>
+  </si>
+  <si>
+    <t>Page has a language assigned</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/language-of-page</t>
   </si>
   <si>
     <t>3.2.3: Consistent Navigation - Level AA</t>
   </si>
   <si>
-    <t>2.4.3: Focus Order - Level A</t>
-  </si>
-  <si>
-    <t>Logical order</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/focus-order</t>
-  </si>
-  <si>
-    <t>2.4.4: Link Purpose (In Context) - Level A</t>
-  </si>
-  <si>
-    <t>Every link’s purpose is clear from its context</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/link-purpose-in-context</t>
-  </si>
-  <si>
-    <t>2.5.1: Pointer Gestures - Level A</t>
-  </si>
-  <si>
-    <t>Let users operate touchscreens with a single finger</t>
+    <t>3.2.1: On Focus - Level A</t>
+  </si>
+  <si>
+    <t>Elements do not change when they receive focus</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/on-focus</t>
+  </si>
+  <si>
+    <t>3.2.2: On Input - Level A</t>
+  </si>
+  <si>
+    <t>Elements do not change when they receive input</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/on-input</t>
+  </si>
+  <si>
+    <t>3.2.6: Consistent Help - Level A</t>
+  </si>
+  <si>
+    <t>Put help in the same place when it is on multiple pages.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/consistent-help</t>
   </si>
   <si>
     <t>https://referrals.radancy.com/dashboard/jobs/active</t>
   </si>
   <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/pointer-gestures.html</t>
+    <t>3.3.1: Error Identification - Level A</t>
+  </si>
+  <si>
+    <t>Clearly identify input errors</t>
   </si>
   <si>
     <t>Global: Primary Navigation Not Accessible</t>
   </si>
   <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/error-identification</t>
+  </si>
+  <si>
     <t xml:space="preserve">The navigation is not currently keyboard accessible and does not include any means to convey the state to assisitve technology users. </t>
   </si>
   <si>
     <t>https://fluffy-adventure-o7451v1.pages.github.io/erp/audit/202510/screengrab/A11YERP001.png</t>
   </si>
   <si>
-    <t>2.5.2: Pointer Cancellation - Level A</t>
-  </si>
-  <si>
-    <t>Reduce accidental activation of controls by making their operation consistent</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/pointer-cancellation</t>
+    <t xml:space="preserve">Auditor:  </t>
+  </si>
+  <si>
+    <t>Michael Spellacy (michael.spellacy@radancy.com)</t>
+  </si>
+  <si>
+    <t>3.3.2: Labels or Instructions - Level A</t>
+  </si>
+  <si>
+    <t>Label elements and give instructions</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/labels-or-instructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implementation Queue:  </t>
   </si>
   <si>
     <t>Implementation Queue</t>
   </si>
   <si>
+    <t>3.3.7: Redundant Entry - Level A</t>
+  </si>
+  <si>
+    <t>Don't ask for the same information twice in the same session.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/redundant-entry</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
     <t>Ready for Production</t>
   </si>
   <si>
-    <t>2.5.3: Label In Name - Level A</t>
-  </si>
-  <si>
-    <t>Let the visual label for controls be a trigger for speech activation.</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/label-in-name</t>
-  </si>
-  <si>
-    <t>2.5.4: Motion Actuation - Level A</t>
-  </si>
-  <si>
-    <t>Don’t rely solely on device motion to control page content</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/motion-actuation</t>
-  </si>
-  <si>
-    <t>3.1.1: Language of Page - Level A</t>
-  </si>
-  <si>
-    <t>Page has a language assigned</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/language-of-page</t>
-  </si>
-  <si>
-    <t>3.2.1: On Focus - Level A</t>
-  </si>
-  <si>
-    <t>Elements do not change when they receive focus</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/on-focus</t>
-  </si>
-  <si>
-    <t>3.2.2: On Input - Level A</t>
-  </si>
-  <si>
-    <t>Elements do not change when they receive input</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/on-input</t>
-  </si>
-  <si>
-    <t>3.2.6: Consistent Help - Level A</t>
-  </si>
-  <si>
-    <t>Put help in the same place when it is on multiple pages.</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/consistent-help</t>
-  </si>
-  <si>
-    <t>3.3.1: Error Identification - Level A</t>
-  </si>
-  <si>
-    <t>Clearly identify input errors</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/error-identification</t>
-  </si>
-  <si>
-    <t>3.3.2: Labels or Instructions - Level A</t>
-  </si>
-  <si>
-    <t>Label elements and give instructions</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/labels-or-instructions</t>
-  </si>
-  <si>
-    <t>3.3.7: Redundant Entry - Level A</t>
-  </si>
-  <si>
-    <t>Don't ask for the same information twice in the same session.</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/redundant-entry</t>
-  </si>
-  <si>
     <t>4.1.1: Parsing (Obsolete in WCAG 2.2, Radancy Best Practice) - Level A</t>
   </si>
   <si>
@@ -651,12 +660,6 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/audio-description-prerecorded</t>
   </si>
   <si>
-    <t xml:space="preserve">Auditor:  </t>
-  </si>
-  <si>
-    <t>Michael Spellacy (michael.spellacy@radancy.com)</t>
-  </si>
-  <si>
     <t>1.3.4: Orientation - Level AA</t>
   </si>
   <si>
@@ -664,9 +667,6 @@
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/orientation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementation Queue:  </t>
   </si>
   <si>
     <t>1.3.5: Identify Input Purpose - Level AA</t>
@@ -706,6 +706,9 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/text-spacing</t>
   </si>
   <si>
+    <t xml:space="preserve">Tools &amp; Testing Methods:  </t>
+  </si>
+  <si>
     <t>1.4.13: Content on Hover or Focus - Level AA</t>
   </si>
   <si>
@@ -713,90 +716,6 @@
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/content-on-hover-or-focus</t>
-  </si>
-  <si>
-    <t>1.4.3: Contrast (Minimum) - Level AA</t>
-  </si>
-  <si>
-    <t>Contrast ratio between text and background is at least 4.5 : 1</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/contrast-minimum</t>
-  </si>
-  <si>
-    <t>1.4.4: Resize text - Level AA</t>
-  </si>
-  <si>
-    <t>Text can be resized to 200% without loss of content or function</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/resize-text</t>
-  </si>
-  <si>
-    <t>1.4.5: Images of Text - Level AA</t>
-  </si>
-  <si>
-    <t>Don’t use images of text</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/images-of-text</t>
-  </si>
-  <si>
-    <t>2.4.11: Focus Not Obscured (Minimum) - Level AA</t>
-  </si>
-  <si>
-    <t>Ensure when an item gets keyboard focus, it is at least partially visible.</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/focus-not-obscured-minimum</t>
-  </si>
-  <si>
-    <t>2.4.5: Multiple Ways - Level AA</t>
-  </si>
-  <si>
-    <t>Offer several ways to find pages</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/multiple-ways</t>
-  </si>
-  <si>
-    <t>2.4.6: Headings and Labels - Level AA</t>
-  </si>
-  <si>
-    <t>Use clear headings and labels</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/headings-and-labels</t>
-  </si>
-  <si>
-    <t>2.4.7: Focus Visible - Level AA</t>
-  </si>
-  <si>
-    <t>Ensure keyboard focus is visible and clear</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/focus-visible</t>
-  </si>
-  <si>
-    <t>2.5.7: Dragging Movements - Level AA</t>
-  </si>
-  <si>
-    <t>For any action that involves dragging, provide a simple pointer alternative.</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/dragging-movements</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tools &amp; Testing Methods:  </t>
-  </si>
-  <si>
-    <t>2.5.8: Target Size (Minimum) - Level AA</t>
-  </si>
-  <si>
-    <t>Ensure targets meet a minimum size or have sufficient spacing around them.</t>
-  </si>
-  <si>
-    <t>https://www.w3.org/WAI/WCAG22/Understanding/target-size-minimum.html</t>
   </si>
   <si>
     <r>
@@ -818,6 +737,90 @@
     </r>
   </si>
   <si>
+    <t>1.4.3: Contrast (Minimum) - Level AA</t>
+  </si>
+  <si>
+    <t>Contrast ratio between text and background is at least 4.5 : 1</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/contrast-minimum</t>
+  </si>
+  <si>
+    <t>1.4.4: Resize text - Level AA</t>
+  </si>
+  <si>
+    <t>Text can be resized to 200% without loss of content or function</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/resize-text</t>
+  </si>
+  <si>
+    <t>1.4.5: Images of Text - Level AA</t>
+  </si>
+  <si>
+    <t>Don’t use images of text</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/images-of-text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accessibility Support:  </t>
+  </si>
+  <si>
+    <t>2.4.11: Focus Not Obscured (Minimum) - Level AA</t>
+  </si>
+  <si>
+    <t>Ensure when an item gets keyboard focus, it is at least partially visible.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/focus-not-obscured-minimum</t>
+  </si>
+  <si>
+    <t>2.4.5: Multiple Ways - Level AA</t>
+  </si>
+  <si>
+    <t>Offer several ways to find pages</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/multiple-ways</t>
+  </si>
+  <si>
+    <t>2.4.6: Headings and Labels - Level AA</t>
+  </si>
+  <si>
+    <t>Use clear headings and labels</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/headings-and-labels</t>
+  </si>
+  <si>
+    <t>2.4.7: Focus Visible - Level AA</t>
+  </si>
+  <si>
+    <t>Ensure keyboard focus is visible and clear</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/focus-visible</t>
+  </si>
+  <si>
+    <t>2.5.7: Dragging Movements - Level AA</t>
+  </si>
+  <si>
+    <t>For any action that involves dragging, provide a simple pointer alternative.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/dragging-movements</t>
+  </si>
+  <si>
+    <t>2.5.8: Target Size (Minimum) - Level AA</t>
+  </si>
+  <si>
+    <t>Ensure targets meet a minimum size or have sufficient spacing around them.</t>
+  </si>
+  <si>
+    <t>https://www.w3.org/WAI/WCAG22/Understanding/target-size-minimum.html</t>
+  </si>
+  <si>
     <t>3.1.2: Language of Parts - Level AA</t>
   </si>
   <si>
@@ -833,9 +836,6 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/consistent-navigation</t>
   </si>
   <si>
-    <t xml:space="preserve">Accessibility Support:  </t>
-  </si>
-  <si>
     <t>3.2.4: Consistent Identification - Level AA</t>
   </si>
   <si>
@@ -863,6 +863,9 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/error-prevention-legal-financial-data</t>
   </si>
   <si>
+    <t xml:space="preserve">Creative Support:  </t>
+  </si>
+  <si>
     <t>3.3.8: Accessible Authentication (Minimum) - Level AA</t>
   </si>
   <si>
@@ -953,15 +956,15 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/visual-presentation</t>
   </si>
   <si>
+    <t xml:space="preserve">Product Engineer: </t>
+  </si>
+  <si>
     <t>1.4.9: Images of Text (No Exception) - Level AAA</t>
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/images-of-text-no-exception</t>
   </si>
   <si>
-    <t xml:space="preserve">Creative Support:  </t>
-  </si>
-  <si>
     <t>2.1.3: Keyboard (No Exception) - Level AAA</t>
   </si>
   <si>
@@ -1019,6 +1022,9 @@
     <t>Allow users to turn off unnecessary motion effects</t>
   </si>
   <si>
+    <t>Product Owner</t>
+  </si>
+  <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/animation-from-interactions</t>
   </si>
   <si>
@@ -1067,9 +1073,6 @@
     <t>https://www.w3.org/WAI/WCAG22/Understanding/link-purpose-link-only</t>
   </si>
   <si>
-    <t xml:space="preserve">Product Engineer: </t>
-  </si>
-  <si>
     <t>2.5.5: Target Size - Level AAA</t>
   </si>
   <si>
@@ -1095,6 +1098,9 @@
   </si>
   <si>
     <t>https://www.w3.org/WAI/WCAG22/Understanding/unusual-words</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSS Support:  </t>
   </si>
   <si>
     <t>3.1.4: Abbreviations - Level AAA</t>
@@ -1185,6 +1191,12 @@
     </r>
   </si>
   <si>
+    <t>Definitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditor Notes:  </t>
+  </si>
+  <si>
     <t>Automated Scan (WAVE)</t>
   </si>
   <si>
@@ -1192,27 +1204,6 @@
   </si>
   <si>
     <t>https://radancy.dev/a11y/#wave</t>
-  </si>
-  <si>
-    <t>https://radancy.dev/a11y/#axe</t>
-  </si>
-  <si>
-    <t>Automated Scan (W3C)</t>
-  </si>
-  <si>
-    <t>https://radancy.dev/a11y/#w3c</t>
-  </si>
-  <si>
-    <t>Product Owner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSS Support:  </t>
-  </si>
-  <si>
-    <t>Definitions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auditor Notes:  </t>
   </si>
   <si>
     <r>
@@ -1240,6 +1231,15 @@
       </rPr>
       <t>.</t>
     </r>
+  </si>
+  <si>
+    <t>https://radancy.dev/a11y/#axe</t>
+  </si>
+  <si>
+    <t>Automated Scan (W3C)</t>
+  </si>
+  <si>
+    <t>https://radancy.dev/a11y/#w3c</t>
   </si>
   <si>
     <t xml:space="preserve">  Prevents access to certain users, but workarounds exist for expert users.</t>
@@ -1345,6 +1345,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -1355,13 +1361,12 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font/>
     <font>
-      <b/>
       <sz val="10.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
     <font>
       <b/>
       <sz val="10.0"/>
@@ -1369,11 +1374,12 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="11.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
@@ -1384,20 +1390,14 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="10.0"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.0"/>
-      <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1413,15 +1413,25 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <u/>
       <sz val="10.0"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="11.0"/>
+      <color rgb="FF434343"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF548DD4"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1430,6 +1440,13 @@
       <name val="Arial"/>
     </font>
     <font>
+      <u/>
+      <sz val="11.0"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11.0"/>
       <color rgb="FF434343"/>
       <name val="Arial"/>
@@ -1441,17 +1458,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color rgb="FF548DD4"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11.0"/>
-      <color rgb="FF434343"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <u/>
       <sz val="10.0"/>
       <color rgb="FF1155CC"/>
@@ -1460,12 +1466,6 @@
     <font>
       <u/>
       <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11.0"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
@@ -1497,14 +1497,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <u/>
       <sz val="11.0"/>
       <color rgb="FF0563C1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1545,6 +1545,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1CD"/>
+        <bgColor rgb="FFB7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF666666"/>
         <bgColor rgb="FF666666"/>
       </patternFill>
@@ -1557,26 +1563,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD9D2E9"/>
+        <bgColor rgb="FFD9D2E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFB7B7B7"/>
         <bgColor rgb="FFB7B7B7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1CD"/>
-        <bgColor rgb="FFB7E1CD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF434343"/>
         <bgColor rgb="FF434343"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9D2E9"/>
-        <bgColor rgb="FFD9D2E9"/>
       </patternFill>
     </fill>
     <fill>
@@ -1679,11 +1679,6 @@
   <borders count="28">
     <border/>
     <border>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -1696,6 +1691,11 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
     </border>
     <border>
       <bottom style="thin">
@@ -1873,221 +1873,218 @@
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="10" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="13" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="14" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="15" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="16" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="17" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="16" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="7" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="12" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="11" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="13" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="14" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="15" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="13" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="6" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf borderId="2" fillId="17" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="17" numFmtId="14" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="10" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="9" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="16" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="16" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="7" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="16" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="16" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="8" fillId="18" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="12" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="16" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="10" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="16" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="19" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="14" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="20" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="16" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="19" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="16" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="17" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="14" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="20" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="16" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="24" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="24" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="17" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="21" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="8" fontId="8" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2099,6 +2096,9 @@
     <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="9" numFmtId="49" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -2106,19 +2106,13 @@
     <xf borderId="4" fillId="20" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="22" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="22" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="23" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="23" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="24" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -2127,11 +2121,17 @@
     <xf borderId="9" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="12" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="12" fontId="29" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="30" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="18" fillId="9" fontId="31" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2159,7 +2159,7 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="24" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="16" fillId="18" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2171,26 +2171,26 @@
     <xf borderId="25" fillId="9" fontId="33" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="21" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="21" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="25" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="2" fillId="20" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="20" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="22" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="22" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="25" fillId="10" fontId="34" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="23" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="23" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="24" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="24" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="9" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -2635,83 +2635,83 @@
   </cols>
   <sheetData>
     <row r="1" ht="60.0" customHeight="1">
-      <c r="A1" s="1"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
-      <c r="Q1" s="5"/>
+      <c r="A1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="6"/>
     </row>
     <row r="2" ht="23.25" customHeight="1">
-      <c r="A2" s="5"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="F2" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" s="9" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="F2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="9" t="s">
+      <c r="H2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="K2" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="O2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" s="9" t="s">
+      <c r="M2" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="11" t="s">
+      <c r="N2" s="12" t="s">
         <v>45</v>
       </c>
+      <c r="O2" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="3" ht="30.0" customHeight="1">
-      <c r="A3" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="15"/>
-      <c r="F3" s="21">
+      <c r="A3" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="22"/>
+      <c r="F3" s="24">
         <f>COUNTIF('Accessibility Report'!X:X,"Fail")</f>
         <v>1</v>
       </c>
-      <c r="G3" s="24">
+      <c r="G3" s="26">
         <f>COUNTIF('Accessibility Report'!X:X,"Pass")</f>
         <v>1</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="28">
         <f>COUNTIF('Accessibility Report'!W:W,"Critical")</f>
         <v>1</v>
       </c>
@@ -2727,260 +2727,260 @@
         <f>COUNTIF('Accessibility Report'!W:W,"Minor")</f>
         <v>1</v>
       </c>
-      <c r="L3" s="32">
+      <c r="L3" s="33">
         <f>COUNTIF('Accessibility Report'!C:C,"A")+COUNTIF('Accessibility Report'!G:G,"A")+COUNTIF('Accessibility Report'!K:K,"A")</f>
         <v>3</v>
       </c>
-      <c r="M3" s="32">
+      <c r="M3" s="33">
         <f>COUNTIF('Accessibility Report'!C:C,"AA")+COUNTIF('Accessibility Report'!G:G,"AA")+COUNTIF('Accessibility Report'!K:K,"AA")</f>
         <v>1</v>
       </c>
-      <c r="N3" s="32">
+      <c r="N3" s="33">
         <f>COUNTIF('Accessibility Report'!C:C,"AAA")+COUNTIF('Accessibility Report'!G:G,"AAA")+COUNTIF('Accessibility Report'!K:K,"AAA")</f>
         <v>0</v>
       </c>
-      <c r="O3" s="37">
+      <c r="O3" s="34">
         <f>COUNTIF('Accessibility Report'!C:C,"BP")+COUNTIF('Accessibility Report'!G:G,"BP")+COUNTIF('Accessibility Report'!K:K,"BP")</f>
         <v>0</v>
       </c>
-      <c r="P3" s="37">
+      <c r="P3" s="34">
         <f>COUNTIF('Accessibility Report'!C:C,"Auto")+COUNTIF('Accessibility Report'!G:G,"Auto")+COUNTIF('Accessibility Report'!K:K,"Auto")</f>
         <v>1</v>
       </c>
-      <c r="Q3" s="40">
+      <c r="Q3" s="37">
         <f>COUNTA('Accessibility Report'!A:A)-1</f>
         <v>2</v>
       </c>
     </row>
     <row r="4" ht="30.0" customHeight="1">
-      <c r="A4" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="B4" s="46">
+      <c r="A4" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="B4" s="40">
         <v>45577.0</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="15"/>
-      <c r="F4" s="49" t="s">
-        <v>96</v>
+      <c r="C4" s="20"/>
+      <c r="D4" s="22"/>
+      <c r="F4" s="41" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" ht="30.0" customHeight="1">
-      <c r="A5" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="15"/>
+      <c r="A5" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="42"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="22"/>
     </row>
     <row r="6" ht="30.0" customHeight="1">
-      <c r="A6" s="51" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" s="50"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="15"/>
-      <c r="F6" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="K6" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L6" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M6" s="9" t="s">
+      <c r="A6" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="42"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="22"/>
+      <c r="F6" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="22"/>
+      <c r="H6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="N6" s="9" t="s">
+      <c r="K6" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" s="9" t="s">
+      <c r="M6" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="Q6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>45</v>
       </c>
+      <c r="O6" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="P6" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q6" s="15" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="7" ht="30.0" customHeight="1">
-      <c r="A7" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="B7" s="56" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="15"/>
-      <c r="F7" s="57" t="s">
-        <v>120</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="58">
+      <c r="A7" s="48" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="22"/>
+      <c r="F7" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="G7" s="6"/>
+      <c r="H7" s="55">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Development Support Traffic", 'Accessibility Report'!W:W, "Critical")
 </f>
         <v>0</v>
       </c>
-      <c r="I7" s="61">
+      <c r="I7" s="57">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Development Support Traffic", 'Accessibility Report'!W:W, "Serious")</f>
         <v>0</v>
       </c>
-      <c r="J7" s="62">
+      <c r="J7" s="58">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Development Support Traffic", 'Accessibility Report'!W:W, "Moderate")</f>
         <v>0</v>
       </c>
-      <c r="K7" s="63">
+      <c r="K7" s="59">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Development Support Traffic", 'Accessibility Report'!W:W, "Minor")</f>
         <v>0</v>
       </c>
-      <c r="L7" s="64">
+      <c r="L7" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"A",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!G:G,"A",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!K:K,"A",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>0</v>
       </c>
-      <c r="M7" s="64">
+      <c r="M7" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AA",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!G:G,"AA",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!K:K,"AA",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>0</v>
       </c>
-      <c r="N7" s="64">
+      <c r="N7" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AAA",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!G:G,"AAA",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!K:K,"AAA",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>0</v>
       </c>
-      <c r="O7" s="64">
+      <c r="O7" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"BP",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!G:G,"BP",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!K:K,"BP",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>0</v>
       </c>
-      <c r="P7" s="64">
+      <c r="P7" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"Auto",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!G:G,"Auto",'Accessibility Report'!Y:Y,"Development Support Traffic")+COUNTIFS('Accessibility Report'!K:K,"Auto",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="69">
         <f>COUNTIFS('Accessibility Report'!B:B,"&lt;&gt;",'Accessibility Report'!Y:Y,"Development Support Traffic")
 </f>
         <v>0</v>
       </c>
     </row>
     <row r="8" ht="30.0" customHeight="1">
-      <c r="A8" s="12" t="s">
-        <v>179</v>
+      <c r="A8" s="17" t="s">
+        <v>159</v>
       </c>
       <c r="B8" s="72" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
+        <v>160</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="22"/>
       <c r="F8" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="58">
+        <v>164</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="55">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Implementation Queue", 'Accessibility Report'!W:W, "Critical")
 </f>
         <v>0</v>
       </c>
-      <c r="I8" s="61">
+      <c r="I8" s="57">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Implementation Queue", 'Accessibility Report'!W:W, "Serious")</f>
         <v>0</v>
       </c>
-      <c r="J8" s="62">
+      <c r="J8" s="58">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Implementation Queue", 'Accessibility Report'!W:W, "Moderate")</f>
         <v>0</v>
       </c>
-      <c r="K8" s="63">
+      <c r="K8" s="59">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Implementation Queue", 'Accessibility Report'!W:W, "Minor")</f>
         <v>1</v>
       </c>
-      <c r="L8" s="64">
+      <c r="L8" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"A",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!G:G,"A",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!K:K,"A",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>1</v>
       </c>
-      <c r="M8" s="64">
+      <c r="M8" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AA",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!G:G,"AA",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!K:K,"AA",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>1</v>
       </c>
-      <c r="N8" s="64">
+      <c r="N8" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AAA",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!G:G,"AAA",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!K:K,"AAA",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>0</v>
       </c>
-      <c r="O8" s="64">
+      <c r="O8" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"BP",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!G:G,"BP",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!K:K,"BP",'Accessibility Report'!Y:Y,"Development Support Traffic")</f>
         <v>0</v>
       </c>
-      <c r="P8" s="64">
+      <c r="P8" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"Auto",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!G:G,"Auto",'Accessibility Report'!Y:Y,"Implementation Queue")+COUNTIFS('Accessibility Report'!K:K,"Auto",'Accessibility Report'!Y:Y,"Implementation Queue")</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="71">
+      <c r="Q8" s="69">
         <f>COUNTIFS('Accessibility Report'!B:B,"&lt;&gt;",'Accessibility Report'!Y:Y,"Implementation Queue")
 </f>
         <v>1</v>
       </c>
     </row>
     <row r="9" ht="30.0" customHeight="1">
-      <c r="A9" s="75" t="s">
-        <v>224</v>
-      </c>
-      <c r="B9" s="76" t="s">
-        <v>228</v>
-      </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="78"/>
-      <c r="F9" s="79" t="s">
-        <v>234</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="58">
+      <c r="A9" s="74" t="s">
+        <v>197</v>
+      </c>
+      <c r="B9" s="75" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="76"/>
+      <c r="D9" s="77"/>
+      <c r="F9" s="78" t="s">
+        <v>211</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="55">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Accessibility Support", 'Accessibility Report'!W:W, "Critical")
 </f>
-        <v>1</v>
-      </c>
-      <c r="I9" s="61">
+        <v>0</v>
+      </c>
+      <c r="I9" s="57">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Accessibility Support", 'Accessibility Report'!W:W, "Serious")</f>
         <v>0</v>
       </c>
-      <c r="J9" s="62">
+      <c r="J9" s="58">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Accessibility Support", 'Accessibility Report'!W:W, "Moderate")</f>
         <v>0</v>
       </c>
-      <c r="K9" s="63">
+      <c r="K9" s="59">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Accessibility Support", 'Accessibility Report'!W:W, "Minor")</f>
         <v>0</v>
       </c>
-      <c r="L9" s="64">
+      <c r="L9" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"A",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!G:G,"A",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!K:K,"A",'Accessibility Report'!Y:Y,"Accessibility Support")</f>
-        <v>2</v>
-      </c>
-      <c r="M9" s="64">
+        <v>0</v>
+      </c>
+      <c r="M9" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AA",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!G:G,"AA",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!K:K,"AA",'Accessibility Report'!Y:Y,"Accessibility Support")</f>
         <v>0</v>
       </c>
-      <c r="N9" s="64">
+      <c r="N9" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AAA",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!G:G,"AAA",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!K:K,"AAA",'Accessibility Report'!Y:Y,"Accessibility Support")</f>
         <v>0</v>
       </c>
-      <c r="O9" s="64">
+      <c r="O9" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"BP",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!G:G,"BP",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!K:K,"BP",'Accessibility Report'!Y:Y,"Accessibility Support")</f>
         <v>0</v>
       </c>
-      <c r="P9" s="64">
+      <c r="P9" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"Auto",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!G:G,"Auto",'Accessibility Report'!Y:Y,"Accessibility Support")+COUNTIFS('Accessibility Report'!K:K,"Auto",'Accessibility Report'!Y:Y,"Accessibility Support")</f>
-        <v>1</v>
-      </c>
-      <c r="Q9" s="71">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="69">
         <f>COUNTIFS('Accessibility Report'!B:B,"&lt;&gt;",'Accessibility Report'!Y:Y,"Accessibility Support")
 </f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="30.0" customHeight="1">
@@ -2988,47 +2988,47 @@
       <c r="B10" s="81"/>
       <c r="D10" s="82"/>
       <c r="F10" s="83" t="s">
-        <v>276</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="58">
+        <v>244</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="55">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Creative Support", 'Accessibility Report'!W:W, "Critical")
 </f>
         <v>0</v>
       </c>
-      <c r="I10" s="61">
+      <c r="I10" s="57">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Creative Support", 'Accessibility Report'!W:W, "Serious")</f>
         <v>0</v>
       </c>
-      <c r="J10" s="62">
+      <c r="J10" s="58">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Creative Support", 'Accessibility Report'!W:W, "Moderate")</f>
         <v>0</v>
       </c>
-      <c r="K10" s="63">
+      <c r="K10" s="59">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Creative Support", 'Accessibility Report'!W:W, "Minor")</f>
         <v>0</v>
       </c>
-      <c r="L10" s="64">
+      <c r="L10" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"A",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!G:G,"A",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!K:K,"A",'Accessibility Report'!Y:Y,"Creative Support")</f>
         <v>0</v>
       </c>
-      <c r="M10" s="64">
+      <c r="M10" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AA",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!G:G,"AA",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!K:K,"AA",'Accessibility Report'!Y:Y,"Creative Support")</f>
         <v>0</v>
       </c>
-      <c r="N10" s="64">
+      <c r="N10" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AAA",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!G:G,"AAA",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!K:K,"AAA",'Accessibility Report'!Y:Y,"Creative Support")</f>
         <v>0</v>
       </c>
-      <c r="O10" s="64">
+      <c r="O10" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"BP",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!G:G,"BP",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!K:K,"BP",'Accessibility Report'!Y:Y,"Creative Support")</f>
         <v>0</v>
       </c>
-      <c r="P10" s="64">
+      <c r="P10" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"Auto",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!G:G,"Auto",'Accessibility Report'!Y:Y,"Creative Support")+COUNTIFS('Accessibility Report'!K:K,"Auto",'Accessibility Report'!Y:Y,"Creative Support")</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="71">
+      <c r="Q10" s="69">
         <f>COUNTIFS('Accessibility Report'!B:B,"&lt;&gt;",'Accessibility Report'!Y:Y,"Creative Support")</f>
         <v>0</v>
       </c>
@@ -3038,47 +3038,47 @@
       <c r="B11" s="81"/>
       <c r="D11" s="82"/>
       <c r="F11" s="84" t="s">
-        <v>312</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="58">
+        <v>275</v>
+      </c>
+      <c r="G11" s="22"/>
+      <c r="H11" s="55">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Engineer", 'Accessibility Report'!W:W, "Critical")
 </f>
         <v>0</v>
       </c>
-      <c r="I11" s="61">
+      <c r="I11" s="57">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Engineer", 'Accessibility Report'!W:W, "Serious")</f>
         <v>0</v>
       </c>
-      <c r="J11" s="62">
+      <c r="J11" s="58">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Engineer", 'Accessibility Report'!W:W, "Moderate")</f>
         <v>0</v>
       </c>
-      <c r="K11" s="63">
+      <c r="K11" s="59">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Engineer", 'Accessibility Report'!W:W, "Minor")</f>
         <v>0</v>
       </c>
-      <c r="L11" s="64">
+      <c r="L11" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"A",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!G:G,"A",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!K:K,"A",'Accessibility Report'!Y:Y,"Product Engineer")</f>
         <v>0</v>
       </c>
-      <c r="M11" s="64">
+      <c r="M11" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AA",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!G:G,"AA",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!K:K,"AA",'Accessibility Report'!Y:Y,"Product Engineer")</f>
         <v>0</v>
       </c>
-      <c r="N11" s="64">
+      <c r="N11" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AAA",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!G:G,"AAA",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!K:K,"AAA",'Accessibility Report'!Y:Y,"Product Engineer")</f>
         <v>0</v>
       </c>
-      <c r="O11" s="64">
+      <c r="O11" s="62">
         <f>COUNTIFS('Accessibility Report'!E:E,"BP",'Accessibility Report'!AA:AA,"Product Engineer")+COUNTIFS('Accessibility Report'!I:I,"BP",'Accessibility Report'!AA:AA,"Product Engineer")+COUNTIFS('Accessibility Report'!M:M,"BP",'Accessibility Report'!AA:AA,"Product Engineer")</f>
         <v>0</v>
       </c>
-      <c r="P11" s="64">
+      <c r="P11" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"Auto",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!G:G,"Auto",'Accessibility Report'!Y:Y,"Product Engineer")+COUNTIFS('Accessibility Report'!K:K,"Auto",'Accessibility Report'!Y:Y,"Product Engineer")</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="71">
+      <c r="Q11" s="69">
         <f>COUNTIFS('Accessibility Report'!B:B,"&lt;&gt;",'Accessibility Report'!Y:Y,"Product Engineer")
 </f>
         <v>0</v>
@@ -3088,48 +3088,48 @@
       <c r="A12" s="80"/>
       <c r="B12" s="81"/>
       <c r="D12" s="82"/>
-      <c r="F12" s="87" t="s">
-        <v>352</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="58">
+      <c r="F12" s="85" t="s">
+        <v>297</v>
+      </c>
+      <c r="G12" s="22"/>
+      <c r="H12" s="55">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Owner", 'Accessibility Report'!W:W, "Critical")
 </f>
         <v>0</v>
       </c>
-      <c r="I12" s="61">
+      <c r="I12" s="57">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Owner", 'Accessibility Report'!W:W, "Serious")</f>
         <v>0</v>
       </c>
-      <c r="J12" s="62">
+      <c r="J12" s="58">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Owner", 'Accessibility Report'!W:W, "Moderate")</f>
         <v>0</v>
       </c>
-      <c r="K12" s="63">
+      <c r="K12" s="59">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "Product Owner", 'Accessibility Report'!W:W, "Minor")</f>
         <v>0</v>
       </c>
-      <c r="L12" s="64">
+      <c r="L12" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"A",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!G:G,"A",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!K:K,"A",'Accessibility Report'!Y:Y,"Product Owner")</f>
         <v>0</v>
       </c>
-      <c r="M12" s="64">
+      <c r="M12" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AA",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!G:G,"AA",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!K:K,"AA",'Accessibility Report'!Y:Y,"Product Owner")</f>
         <v>0</v>
       </c>
-      <c r="N12" s="64">
+      <c r="N12" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AAA",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!G:G,"AAA",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!K:K,"AAA",'Accessibility Report'!Y:Y,"Product Owner")</f>
         <v>0</v>
       </c>
-      <c r="O12" s="64">
+      <c r="O12" s="62">
         <f>COUNTIFS('Accessibility Report'!E:E,"BP",'Accessibility Report'!AA:AA,"Product Owner")+COUNTIFS('Accessibility Report'!I:I,"BP",'Accessibility Report'!AA:AA,"Product Owner")+COUNTIFS('Accessibility Report'!M:M,"BP",'Accessibility Report'!AA:AA,"Product Owner")</f>
         <v>0</v>
       </c>
-      <c r="P12" s="64">
+      <c r="P12" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"Auto",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!G:G,"Auto",'Accessibility Report'!Y:Y,"Product Owner")+COUNTIFS('Accessibility Report'!K:K,"Auto",'Accessibility Report'!Y:Y,"Product Owner")</f>
         <v>0</v>
       </c>
-      <c r="Q12" s="71">
+      <c r="Q12" s="69">
         <f>COUNTIFS('Accessibility Report'!B:B,"&lt;&gt;",'Accessibility Report'!Y:Y,"Product Owner")
 </f>
         <v>0</v>
@@ -3139,75 +3139,75 @@
       <c r="A13" s="80"/>
       <c r="B13" s="81"/>
       <c r="D13" s="82"/>
-      <c r="F13" s="88" t="s">
-        <v>353</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="58">
+      <c r="F13" s="86" t="s">
+        <v>323</v>
+      </c>
+      <c r="G13" s="22"/>
+      <c r="H13" s="55">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "CSS Support", 'Accessibility Report'!W:W, "Critical")
 </f>
         <v>0</v>
       </c>
-      <c r="I13" s="61">
+      <c r="I13" s="57">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "CSS Support", 'Accessibility Report'!W:W, "Serious")</f>
         <v>0</v>
       </c>
-      <c r="J13" s="62">
+      <c r="J13" s="58">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "CSS Support", 'Accessibility Report'!W:W, "Moderate")</f>
         <v>0</v>
       </c>
-      <c r="K13" s="63">
+      <c r="K13" s="59">
         <f>COUNTIFS('Accessibility Report'!Y:Y, "CSS Support", 'Accessibility Report'!W:W, "Minor")</f>
         <v>0</v>
       </c>
-      <c r="L13" s="64">
+      <c r="L13" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"A",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!G:G,"A",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!K:K,"A",'Accessibility Report'!Y:Y,"CSS Support")</f>
         <v>0</v>
       </c>
-      <c r="M13" s="64">
+      <c r="M13" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AA",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!G:G,"AA",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!J:J,"AA",'Accessibility Report'!Y:Y,"CSS Support")</f>
         <v>0</v>
       </c>
-      <c r="N13" s="64">
+      <c r="N13" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"AAA",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!G:G,"AAA",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!K:K,"AAA",'Accessibility Report'!Y:Y,"CSS Support")</f>
         <v>0</v>
       </c>
-      <c r="O13" s="64">
+      <c r="O13" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"BP",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!G:G,"BP",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!K:K,"BP",'Accessibility Report'!Y:Y,"CSS Support")</f>
         <v>0</v>
       </c>
-      <c r="P13" s="64">
+      <c r="P13" s="62">
         <f>COUNTIFS('Accessibility Report'!C:C,"Auto",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!G:G,"Auto",'Accessibility Report'!Y:Y,"CSS Support")+COUNTIFS('Accessibility Report'!K:K,"Auto",'Accessibility Report'!Y:Y,"CSS Support")</f>
         <v>0</v>
       </c>
-      <c r="Q13" s="71">
+      <c r="Q13" s="69">
         <f>COUNTIFS('Accessibility Report'!B:B,"&lt;&gt;",'Accessibility Report'!Y:Y,"CSS Support")
 </f>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="41.25" customHeight="1">
-      <c r="A14" s="89"/>
-      <c r="B14" s="90"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="91"/>
-      <c r="F14" s="49" t="s">
-        <v>354</v>
+      <c r="A14" s="87"/>
+      <c r="B14" s="88"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="89"/>
+      <c r="F14" s="41" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="15" ht="30.0" customHeight="1">
-      <c r="A15" s="92" t="s">
-        <v>355</v>
-      </c>
-      <c r="B15" s="93"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="78"/>
-      <c r="F15" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="15"/>
+      <c r="A15" s="90" t="s">
+        <v>349</v>
+      </c>
+      <c r="B15" s="92"/>
+      <c r="C15" s="76"/>
+      <c r="D15" s="77"/>
+      <c r="F15" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="22"/>
       <c r="H15" s="95" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="I15" s="96"/>
       <c r="J15" s="96"/>
@@ -3224,9 +3224,9 @@
       <c r="B16" s="81"/>
       <c r="D16" s="82"/>
       <c r="F16" s="98" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="15"/>
+        <v>39</v>
+      </c>
+      <c r="G16" s="22"/>
       <c r="H16" s="99" t="s">
         <v>357</v>
       </c>
@@ -3245,9 +3245,9 @@
       <c r="B17" s="81"/>
       <c r="D17" s="82"/>
       <c r="F17" s="102" t="s">
-        <v>29</v>
-      </c>
-      <c r="G17" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="G17" s="22"/>
       <c r="H17" s="103" t="s">
         <v>358</v>
       </c>
@@ -3257,18 +3257,18 @@
       <c r="B18" s="81"/>
       <c r="D18" s="82"/>
       <c r="F18" s="104" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="15"/>
+        <v>41</v>
+      </c>
+      <c r="G18" s="22"/>
       <c r="H18" s="103" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="19" ht="82.5" customHeight="1">
-      <c r="A19" s="89"/>
-      <c r="B19" s="90"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="91"/>
+      <c r="A19" s="87"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="89"/>
       <c r="F19" s="105" t="s">
         <v>360</v>
       </c>
@@ -3288,8 +3288,8 @@
         <f>SUMIF('Accessibility Report'!Y:Y, "Development Support Traffic", 'Accessibility Report'!AF:AF)</f>
         <v>0</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="15"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="22"/>
       <c r="F21" s="110"/>
       <c r="Q21" s="106"/>
     </row>
@@ -3301,21 +3301,21 @@
         <f>SUMIF('Accessibility Report'!Y:Y, "Implementation Queue", 'Accessibility Report'!AF:AF)</f>
         <v>3</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="15"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="22"/>
       <c r="F22" s="112"/>
       <c r="Q22" s="106"/>
     </row>
     <row r="23" ht="30.0" customHeight="1">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="39" t="s">
         <v>364</v>
       </c>
       <c r="B23" s="109">
         <f>SUMIF('Accessibility Report'!Y:Y, "Accessibility Support", 'Accessibility Report'!AF:AF)</f>
-        <v>1.25</v>
-      </c>
-      <c r="C23" s="14"/>
-      <c r="D23" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="22"/>
       <c r="F23" s="112"/>
       <c r="Q23" s="106"/>
     </row>
@@ -3327,21 +3327,21 @@
         <f>SUMIF('Accessibility Report'!Y:Y, "Creative Support", 'Accessibility Report'!AF:AF)</f>
         <v>0</v>
       </c>
-      <c r="C24" s="14"/>
-      <c r="D24" s="15"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="22"/>
       <c r="F24" s="112"/>
       <c r="Q24" s="106"/>
     </row>
     <row r="25" ht="30.0" customHeight="1">
       <c r="A25" s="114" t="s">
-        <v>312</v>
-      </c>
-      <c r="B25" s="56">
+        <v>275</v>
+      </c>
+      <c r="B25" s="52">
         <f>SUMIF('Accessibility Report'!Y:Y, "Product Engineer", 'Accessibility Report'!AF:AF)</f>
         <v>0</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="15"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="22"/>
       <c r="F25" s="115" t="s">
         <v>366</v>
       </c>
@@ -3349,14 +3349,14 @@
     </row>
     <row r="26" ht="30.0" customHeight="1">
       <c r="A26" s="116" t="s">
-        <v>352</v>
-      </c>
-      <c r="B26" s="56">
+        <v>297</v>
+      </c>
+      <c r="B26" s="52">
         <f>SUMIF('Accessibility Report'!Y:Y, "Product Owner", 'Accessibility Report'!AF:AF)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="14"/>
-      <c r="D26" s="15"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="22"/>
       <c r="F26" s="112"/>
       <c r="Q26" s="106"/>
     </row>
@@ -3368,8 +3368,8 @@
         <f>SUMIF('Accessibility Report'!Y:Y, "CSS Support", 'Accessibility Report'!AF:AF)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="14"/>
-      <c r="D27" s="15"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="22"/>
       <c r="F27" s="112"/>
       <c r="Q27" s="106"/>
     </row>
@@ -3381,8 +3381,8 @@
         <f>SUM('Accessibility Report'!AF:AF)</f>
         <v>4.25</v>
       </c>
-      <c r="C28" s="14"/>
-      <c r="D28" s="15"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="22"/>
       <c r="E28" s="119"/>
       <c r="F28" s="120"/>
       <c r="G28" s="96"/>
@@ -3504,111 +3504,111 @@
   </cols>
   <sheetData>
     <row r="1" ht="41.25" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="X1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="Y1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Z1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="AB1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AC1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AE1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AA1" s="3" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="AB1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC1" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD1" s="3" t="s">
+      <c r="B2" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="AE1" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="AF1" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B2" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="23" t="str">
+      <c r="C2" s="21" t="str">
         <f>IFERROR(VLOOKUP(B2,WCAGLookup,2,FALSE),"")</f>
         <v>A</v>
       </c>
@@ -3616,14 +3616,14 @@
         <f>IFERROR(VLOOKUP(B2,WCAGLookup,3,FALSE),"")</f>
         <v>Provide text alternatives for non-text content</v>
       </c>
-      <c r="E2" s="28" t="str">
+      <c r="E2" s="27" t="str">
         <f>IFERROR(VLOOKUP(B2,WCAGLookup,4,FALSE),"")</f>
         <v>https://www.w3.org/WAI/WCAG22/Understanding/non-text-content</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G2" s="23" t="str">
+      <c r="F2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="21" t="str">
         <f>IFERROR(VLOOKUP(F2,WCAGLookup,2,FALSE),"")</f>
         <v>A</v>
       </c>
@@ -3631,14 +3631,14 @@
         <f>IFERROR(VLOOKUP(F2,WCAGLookup,3,FALSE),"")</f>
         <v>Build all elements for accessibility</v>
       </c>
-      <c r="I2" s="28" t="str">
+      <c r="I2" s="27" t="str">
         <f>IFERROR(VLOOKUP(F2,WCAGLookup,4,FALSE),"")</f>
         <v>https://www.w3.org/WAI/WCAG22/Understanding/name-role-value</v>
       </c>
-      <c r="J2" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="K2" s="23" t="str">
+      <c r="J2" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="21" t="str">
         <f>IFERROR(VLOOKUP(J2,WCAGLookup,2,FALSE),"")</f>
         <v>Auto</v>
       </c>
@@ -3646,58 +3646,58 @@
         <f>IFERROR(VLOOKUP(J2,WCAGLookup,3,FALSE),"")</f>
         <v>Issue found in automated scan and must be addressed. All errors must be fixed. Warnings, if not critical to access can be dismissed, but it is considered good form to address them when possible.</v>
       </c>
-      <c r="M2" s="28" t="str">
+      <c r="M2" s="27" t="str">
         <f>IFERROR(VLOOKUP(J2,WCAGLookup,4,FALSE),"")</f>
         <v>https://radancy.dev/a11y/#axe</v>
       </c>
-      <c r="N2" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="O2" s="35" t="s">
-        <v>80</v>
-      </c>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35" t="s">
-        <v>82</v>
-      </c>
-      <c r="R2" s="36"/>
-      <c r="S2" s="34" t="s">
+      <c r="N2" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="O2" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="R2" s="38"/>
+      <c r="S2" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="T2" s="47"/>
+      <c r="U2" s="49"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="X2" s="56" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y2" s="47" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z2" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA2" s="51"/>
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="61">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="T2" s="38"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="41"/>
-      <c r="W2" s="45" t="s">
-        <v>23</v>
-      </c>
-      <c r="X2" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="Y2" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="Z2" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="AA2" s="41"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="54">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="C3" s="23" t="str">
+      <c r="C3" s="21" t="str">
         <f>IFERROR(VLOOKUP(B3,WCAGLookup,2,FALSE),"")</f>
         <v>A</v>
       </c>
@@ -3705,14 +3705,14 @@
         <f>IFERROR(VLOOKUP(B3,WCAGLookup,3,FALSE),"")</f>
         <v>Accessible by keyboard only</v>
       </c>
-      <c r="E3" s="28" t="str">
+      <c r="E3" s="27" t="str">
         <f>IFERROR(VLOOKUP(B3,WCAGLookup,4,FALSE),"")</f>
         <v>https://www.w3.org/WAI/WCAG22/Understanding/keyboard</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="23" t="str">
+      <c r="F3" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="G3" s="21" t="str">
         <f>IFERROR(VLOOKUP(F3,WCAGLookup,2,FALSE),"")</f>
         <v>AA</v>
       </c>
@@ -3720,14 +3720,14 @@
         <f>IFERROR(VLOOKUP(F3,WCAGLookup,3,FALSE),"")</f>
         <v>Use menus consistently</v>
       </c>
-      <c r="I3" s="28" t="str">
+      <c r="I3" s="27" t="str">
         <f>IFERROR(VLOOKUP(F3,WCAGLookup,4,FALSE),"")</f>
         <v>https://www.w3.org/WAI/WCAG22/Understanding/consistent-navigation</v>
       </c>
-      <c r="J3" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" s="23" t="str">
+      <c r="J3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="21" t="str">
         <f>IFERROR(VLOOKUP(J3,WCAGLookup,2,FALSE),"")</f>
         <v/>
       </c>
@@ -3735,47 +3735,47 @@
         <f>IFERROR(VLOOKUP(J3,WCAGLookup,3,FALSE),"")</f>
         <v/>
       </c>
-      <c r="M3" s="28" t="str">
+      <c r="M3" s="27" t="str">
         <f>IFERROR(VLOOKUP(J3,WCAGLookup,4,FALSE),"")</f>
         <v/>
       </c>
-      <c r="N3" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="R3" s="36"/>
-      <c r="S3" s="60" t="s">
-        <v>134</v>
-      </c>
-      <c r="T3" s="38"/>
-      <c r="U3" s="39"/>
-      <c r="V3" s="41"/>
-      <c r="W3" s="45" t="s">
-        <v>31</v>
-      </c>
-      <c r="X3" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="38" t="s">
-        <v>138</v>
-      </c>
-      <c r="Z3" s="38" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="38"/>
-      <c r="AC3" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="AD3" s="39"/>
-      <c r="AE3" s="39"/>
-      <c r="AF3" s="54">
+      <c r="N3" s="67" t="s">
+        <v>152</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="R3" s="38"/>
+      <c r="S3" s="70" t="s">
+        <v>158</v>
+      </c>
+      <c r="T3" s="47"/>
+      <c r="U3" s="49"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="X3" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z3" s="47" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA3" s="51"/>
+      <c r="AB3" s="47"/>
+      <c r="AC3" s="60" t="s">
+        <v>170</v>
+      </c>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="61">
         <v>3.0</v>
       </c>
     </row>
@@ -3939,1305 +3939,1305 @@
   </cols>
   <sheetData>
     <row r="1" ht="41.25" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B1" s="18" t="s">
+    </row>
+    <row r="2" ht="30.75" customHeight="1">
+      <c r="A2" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="18" t="s">
+      <c r="B2" s="16" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="2" ht="30.75" customHeight="1">
-      <c r="A2" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>47</v>
+      <c r="C2" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>74</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="D19" s="23" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="45" t="s">
+        <v>126</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="D22" s="50" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" s="50" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="D24" s="50" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="45" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="46" t="s">
+        <v>137</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="63" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="D29" s="66" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B30" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="68" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="71" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="68" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" s="71" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="63" t="s">
+        <v>166</v>
+      </c>
+      <c r="B32" s="64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="D32" s="66" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="46" t="s">
+        <v>189</v>
+      </c>
+      <c r="D39" s="50" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" s="50" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="45" t="s">
+        <v>194</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" s="50" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="D42" s="50" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="79" t="s">
+        <v>212</v>
+      </c>
+      <c r="B46" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46" s="68" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" s="71" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C47" s="68" t="s">
+        <v>216</v>
+      </c>
+      <c r="D47" s="71" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B48" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C48" s="68" t="s">
+        <v>219</v>
+      </c>
+      <c r="D48" s="71" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B49" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C49" s="68" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" s="71" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="63" t="s">
+        <v>224</v>
+      </c>
+      <c r="B50" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C50" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="D50" s="66" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="63" t="s">
+        <v>227</v>
+      </c>
+      <c r="B51" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="D51" s="66" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B52" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="68" t="s">
+        <v>231</v>
+      </c>
+      <c r="D52" s="71" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="B53" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C53" s="68" t="s">
+        <v>233</v>
+      </c>
+      <c r="D53" s="71" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B54" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C54" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="71" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B55" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" s="71" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B56" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="68" t="s">
+        <v>242</v>
+      </c>
+      <c r="D56" s="71" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="B57" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C57" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="D57" s="66" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="14" t="s">
+        <v>248</v>
+      </c>
+      <c r="B58" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="C58" s="68" t="s">
+        <v>249</v>
+      </c>
+      <c r="D58" s="71" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="45" t="s">
+        <v>251</v>
+      </c>
+      <c r="B59" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C59" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="D59" s="66" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="45" t="s">
+        <v>254</v>
+      </c>
+      <c r="B60" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" s="65" t="s">
+        <v>255</v>
+      </c>
+      <c r="D60" s="66" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="45" t="s">
+        <v>257</v>
+      </c>
+      <c r="B61" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" s="65" t="s">
+        <v>258</v>
+      </c>
+      <c r="D61" s="66" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="45" t="s">
+        <v>260</v>
+      </c>
+      <c r="B62" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="65" t="s">
+        <v>261</v>
+      </c>
+      <c r="D62" s="66" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="B63" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C63" s="68" t="s">
+        <v>264</v>
+      </c>
+      <c r="D63" s="71" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="45" t="s">
+        <v>266</v>
+      </c>
+      <c r="B64" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C64" s="65" t="s">
+        <v>267</v>
+      </c>
+      <c r="D64" s="66" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="B65" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C65" s="65" t="s">
+        <v>270</v>
+      </c>
+      <c r="D65" s="66" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="45" t="s">
+        <v>272</v>
+      </c>
+      <c r="B66" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C66" s="65" t="s">
+        <v>273</v>
+      </c>
+      <c r="D66" s="66" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="45" t="s">
+        <v>276</v>
+      </c>
+      <c r="B67" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C67" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="D67" s="66" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="45" t="s">
+        <v>278</v>
+      </c>
+      <c r="B68" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C68" s="65" t="s">
+        <v>279</v>
+      </c>
+      <c r="D68" s="66" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="B69" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C69" s="65" t="s">
+        <v>282</v>
+      </c>
+      <c r="D69" s="66" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="45" t="s">
+        <v>284</v>
+      </c>
+      <c r="B70" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" s="65" t="s">
+        <v>285</v>
+      </c>
+      <c r="D70" s="66" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="B71" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C71" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="D71" s="66" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="45" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C72" s="65" t="s">
+        <v>291</v>
+      </c>
+      <c r="D72" s="66" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="45" t="s">
+        <v>293</v>
+      </c>
+      <c r="B73" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C73" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="D73" s="66" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="45" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C74" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="D74" s="66" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="45" t="s">
+        <v>299</v>
+      </c>
+      <c r="B75" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="D75" s="66" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="79" t="s">
+        <v>302</v>
+      </c>
+      <c r="B76" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="68" t="s">
+        <v>303</v>
+      </c>
+      <c r="D76" s="71" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="79" t="s">
+        <v>305</v>
+      </c>
+      <c r="B77" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C77" s="68" t="s">
+        <v>306</v>
+      </c>
+      <c r="D77" s="71" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="45" t="s">
+        <v>308</v>
+      </c>
+      <c r="B78" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C78" s="65" t="s">
+        <v>309</v>
+      </c>
+      <c r="D78" s="66" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="45" t="s">
+        <v>311</v>
+      </c>
+      <c r="B79" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C79" s="65" t="s">
+        <v>312</v>
+      </c>
+      <c r="D79" s="66" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="45" t="s">
+        <v>314</v>
+      </c>
+      <c r="B80" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C80" s="65" t="s">
+        <v>315</v>
+      </c>
+      <c r="D80" s="66" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
+      <c r="A81" s="45" t="s">
+        <v>317</v>
+      </c>
+      <c r="B81" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C81" s="65" t="s">
+        <v>318</v>
+      </c>
+      <c r="D81" s="66" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="45" t="s">
+        <v>320</v>
+      </c>
+      <c r="B82" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C82" s="65" t="s">
+        <v>321</v>
+      </c>
+      <c r="D82" s="66" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="A83" s="45" t="s">
+        <v>324</v>
+      </c>
+      <c r="B83" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C83" s="65" t="s">
+        <v>325</v>
+      </c>
+      <c r="D83" s="66" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="A84" s="45" t="s">
+        <v>327</v>
+      </c>
+      <c r="B84" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C84" s="65" t="s">
+        <v>328</v>
+      </c>
+      <c r="D84" s="66" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="A85" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="B85" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C85" s="65" t="s">
+        <v>331</v>
+      </c>
+      <c r="D85" s="66" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="A86" s="45" t="s">
+        <v>333</v>
+      </c>
+      <c r="B86" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" s="65" t="s">
+        <v>334</v>
+      </c>
+      <c r="D86" s="66" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="A87" s="45" t="s">
+        <v>336</v>
+      </c>
+      <c r="B87" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C87" s="65" t="s">
+        <v>337</v>
+      </c>
+      <c r="D87" s="66" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="A88" s="45" t="s">
+        <v>339</v>
+      </c>
+      <c r="B88" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C88" s="65" t="s">
+        <v>340</v>
+      </c>
+      <c r="D88" s="66" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="A89" s="63" t="s">
+        <v>342</v>
+      </c>
+      <c r="B89" s="64" t="s">
+        <v>45</v>
+      </c>
+      <c r="C89" s="65" t="s">
+        <v>343</v>
+      </c>
+      <c r="D89" s="66" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="A90" s="63" t="s">
+        <v>345</v>
+      </c>
+      <c r="B90" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C90" s="65" t="s">
+        <v>346</v>
+      </c>
+      <c r="D90" s="91" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="A91" s="63" t="s">
+        <v>350</v>
+      </c>
+      <c r="B91" s="64" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="19" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="19" t="s">
-        <v>67</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="33" t="s">
+      <c r="C91" s="65" t="s">
+        <v>351</v>
+      </c>
+      <c r="D91" s="94" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="A92" s="63" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="27" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="27" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="42" t="s">
-        <v>92</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="48" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="D16" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D18" s="27" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="B19" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B20" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" s="27" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="D21" s="27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="48" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="42" t="s">
-        <v>135</v>
-      </c>
-      <c r="B23" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C23" s="44" t="s">
-        <v>136</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="42" t="s">
-        <v>141</v>
-      </c>
-      <c r="B24" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="D24" s="48" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="42" t="s">
-        <v>144</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>147</v>
-      </c>
-      <c r="B26" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C26" s="22" t="s">
-        <v>148</v>
-      </c>
-      <c r="D26" s="27" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="19" t="s">
-        <v>150</v>
-      </c>
-      <c r="B27" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>151</v>
-      </c>
-      <c r="D27" s="27" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C28" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="D28" s="27" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="65" t="s">
-        <v>156</v>
-      </c>
-      <c r="B29" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C29" s="67" t="s">
-        <v>157</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="B30" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" s="69" t="s">
-        <v>160</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B31" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C31" s="69" t="s">
-        <v>163</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="65" t="s">
-        <v>165</v>
-      </c>
-      <c r="B32" s="66" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="67" t="s">
-        <v>166</v>
-      </c>
-      <c r="D32" s="68" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="B33" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="D33" s="27" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>171</v>
-      </c>
-      <c r="D34" s="27" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="22" t="s">
-        <v>174</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="19" t="s">
-        <v>181</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C37" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="D37" s="27" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="D38" s="27" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="42" t="s">
-        <v>188</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="D39" s="48" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="42" t="s">
-        <v>191</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C40" s="44" t="s">
-        <v>192</v>
-      </c>
-      <c r="D40" s="48" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="B41" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="D41" s="48" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="42" t="s">
-        <v>197</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C42" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="D42" s="48" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="19" t="s">
-        <v>200</v>
-      </c>
-      <c r="B43" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="D43" s="27" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="19" t="s">
-        <v>203</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="D44" s="27" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="19" t="s">
-        <v>206</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="D45" s="27" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="74" t="s">
-        <v>209</v>
-      </c>
-      <c r="B46" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="69" t="s">
-        <v>210</v>
-      </c>
-      <c r="D46" s="70" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="19" t="s">
-        <v>212</v>
-      </c>
-      <c r="B47" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="69" t="s">
-        <v>213</v>
-      </c>
-      <c r="D47" s="70" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="B48" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C48" s="69" t="s">
-        <v>216</v>
-      </c>
-      <c r="D48" s="70" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="B49" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" s="69" t="s">
-        <v>219</v>
-      </c>
-      <c r="D49" s="70" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="65" t="s">
-        <v>221</v>
-      </c>
-      <c r="B50" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="67" t="s">
-        <v>222</v>
-      </c>
-      <c r="D50" s="68" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="65" t="s">
-        <v>225</v>
-      </c>
-      <c r="B51" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="D51" s="68" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="19" t="s">
-        <v>229</v>
-      </c>
-      <c r="B52" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="69" t="s">
-        <v>230</v>
-      </c>
-      <c r="D52" s="70" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="19" t="s">
-        <v>121</v>
-      </c>
-      <c r="B53" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C53" s="69" t="s">
-        <v>232</v>
-      </c>
-      <c r="D53" s="70" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="19" t="s">
-        <v>235</v>
-      </c>
-      <c r="B54" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C54" s="69" t="s">
-        <v>236</v>
-      </c>
-      <c r="D54" s="70" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B55" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C55" s="69" t="s">
-        <v>239</v>
-      </c>
-      <c r="D55" s="70" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="19" t="s">
-        <v>241</v>
-      </c>
-      <c r="B56" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C56" s="69" t="s">
-        <v>242</v>
-      </c>
-      <c r="D56" s="70" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="65" t="s">
-        <v>244</v>
-      </c>
-      <c r="B57" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" s="67" t="s">
-        <v>245</v>
-      </c>
-      <c r="D57" s="68" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="19" t="s">
-        <v>247</v>
-      </c>
-      <c r="B58" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="C58" s="69" t="s">
-        <v>248</v>
-      </c>
-      <c r="D58" s="70" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="B59" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C59" s="67" t="s">
-        <v>251</v>
-      </c>
-      <c r="D59" s="68" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="42" t="s">
-        <v>253</v>
-      </c>
-      <c r="B60" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C60" s="67" t="s">
-        <v>254</v>
-      </c>
-      <c r="D60" s="68" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="42" t="s">
-        <v>256</v>
-      </c>
-      <c r="B61" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C61" s="67" t="s">
-        <v>257</v>
-      </c>
-      <c r="D61" s="68" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="42" t="s">
-        <v>259</v>
-      </c>
-      <c r="B62" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C62" s="67" t="s">
-        <v>260</v>
-      </c>
-      <c r="D62" s="68" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="19" t="s">
-        <v>262</v>
-      </c>
-      <c r="B63" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C63" s="69" t="s">
-        <v>263</v>
-      </c>
-      <c r="D63" s="70" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="42" t="s">
-        <v>265</v>
-      </c>
-      <c r="B64" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C64" s="67" t="s">
-        <v>266</v>
-      </c>
-      <c r="D64" s="68" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="42" t="s">
-        <v>268</v>
-      </c>
-      <c r="B65" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C65" s="67" t="s">
-        <v>269</v>
-      </c>
-      <c r="D65" s="68" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="42" t="s">
-        <v>271</v>
-      </c>
-      <c r="B66" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C66" s="67" t="s">
-        <v>272</v>
-      </c>
-      <c r="D66" s="68" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="B67" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C67" s="67" t="s">
-        <v>207</v>
-      </c>
-      <c r="D67" s="68" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="42" t="s">
-        <v>277</v>
-      </c>
-      <c r="B68" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C68" s="67" t="s">
-        <v>278</v>
-      </c>
-      <c r="D68" s="68" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="42" t="s">
-        <v>280</v>
-      </c>
-      <c r="B69" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C69" s="67" t="s">
-        <v>281</v>
-      </c>
-      <c r="D69" s="68" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="42" t="s">
-        <v>283</v>
-      </c>
-      <c r="B70" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C70" s="67" t="s">
-        <v>284</v>
-      </c>
-      <c r="D70" s="68" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="42" t="s">
-        <v>286</v>
-      </c>
-      <c r="B71" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C71" s="67" t="s">
-        <v>287</v>
-      </c>
-      <c r="D71" s="68" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="42" t="s">
-        <v>289</v>
-      </c>
-      <c r="B72" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C72" s="67" t="s">
-        <v>290</v>
-      </c>
-      <c r="D72" s="68" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="B73" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C73" s="67" t="s">
-        <v>109</v>
-      </c>
-      <c r="D73" s="68" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="B74" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C74" s="67" t="s">
-        <v>295</v>
-      </c>
-      <c r="D74" s="68" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="42" t="s">
-        <v>297</v>
-      </c>
-      <c r="B75" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C75" s="67" t="s">
-        <v>298</v>
-      </c>
-      <c r="D75" s="68" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="74" t="s">
-        <v>300</v>
-      </c>
-      <c r="B76" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" s="69" t="s">
-        <v>301</v>
-      </c>
-      <c r="D76" s="70" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="74" t="s">
-        <v>303</v>
-      </c>
-      <c r="B77" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C77" s="69" t="s">
-        <v>304</v>
-      </c>
-      <c r="D77" s="70" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="42" t="s">
-        <v>306</v>
-      </c>
-      <c r="B78" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C78" s="67" t="s">
-        <v>307</v>
-      </c>
-      <c r="D78" s="68" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="42" t="s">
-        <v>309</v>
-      </c>
-      <c r="B79" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C79" s="67" t="s">
-        <v>310</v>
-      </c>
-      <c r="D79" s="68" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="42" t="s">
-        <v>313</v>
-      </c>
-      <c r="B80" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C80" s="67" t="s">
-        <v>314</v>
-      </c>
-      <c r="D80" s="68" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="42" t="s">
-        <v>316</v>
-      </c>
-      <c r="B81" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C81" s="67" t="s">
-        <v>317</v>
-      </c>
-      <c r="D81" s="68" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="42" t="s">
-        <v>319</v>
-      </c>
-      <c r="B82" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C82" s="67" t="s">
-        <v>320</v>
-      </c>
-      <c r="D82" s="68" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="42" t="s">
-        <v>322</v>
-      </c>
-      <c r="B83" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C83" s="67" t="s">
-        <v>323</v>
-      </c>
-      <c r="D83" s="68" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="42" t="s">
-        <v>325</v>
-      </c>
-      <c r="B84" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C84" s="67" t="s">
-        <v>326</v>
-      </c>
-      <c r="D84" s="68" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="42" t="s">
-        <v>328</v>
-      </c>
-      <c r="B85" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C85" s="67" t="s">
-        <v>329</v>
-      </c>
-      <c r="D85" s="68" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="42" t="s">
-        <v>331</v>
-      </c>
-      <c r="B86" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C86" s="67" t="s">
-        <v>332</v>
-      </c>
-      <c r="D86" s="68" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="42" t="s">
-        <v>334</v>
-      </c>
-      <c r="B87" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C87" s="67" t="s">
-        <v>335</v>
-      </c>
-      <c r="D87" s="68" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="42" t="s">
-        <v>337</v>
-      </c>
-      <c r="B88" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C88" s="67" t="s">
-        <v>338</v>
-      </c>
-      <c r="D88" s="68" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="65" t="s">
-        <v>340</v>
-      </c>
-      <c r="B89" s="66" t="s">
-        <v>42</v>
-      </c>
-      <c r="C89" s="67" t="s">
-        <v>341</v>
-      </c>
-      <c r="D89" s="68" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="65" t="s">
-        <v>343</v>
-      </c>
-      <c r="B90" s="66" t="s">
-        <v>43</v>
-      </c>
-      <c r="C90" s="67" t="s">
-        <v>344</v>
-      </c>
-      <c r="D90" s="85" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="65" t="s">
-        <v>346</v>
-      </c>
-      <c r="B91" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="C91" s="67" t="s">
-        <v>347</v>
-      </c>
-      <c r="D91" s="86" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="65" t="s">
-        <v>66</v>
-      </c>
-      <c r="B92" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="C92" s="67" t="s">
-        <v>347</v>
-      </c>
-      <c r="D92" s="68" t="s">
-        <v>349</v>
+      <c r="B92" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C92" s="65" t="s">
+        <v>351</v>
+      </c>
+      <c r="D92" s="66" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="65" t="s">
-        <v>350</v>
-      </c>
-      <c r="B93" s="66" t="s">
-        <v>44</v>
-      </c>
-      <c r="C93" s="67" t="s">
-        <v>347</v>
-      </c>
-      <c r="D93" s="68" t="s">
+      <c r="A93" s="63" t="s">
+        <v>355</v>
+      </c>
+      <c r="B93" s="64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C93" s="65" t="s">
         <v>351</v>
+      </c>
+      <c r="D93" s="66" t="s">
+        <v>356</v>
       </c>
     </row>
   </sheetData>
